--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.21750078210061</v>
+        <v>2.79784387709135</v>
       </c>
       <c r="D2" t="n">
-        <v>17.81731444377822</v>
+        <v>2.895313597113961</v>
       </c>
       <c r="E2" t="n">
-        <v>7.014961156559708</v>
+        <v>1.139931187940953</v>
       </c>
       <c r="F2" t="n">
-        <v>1.472430042017145</v>
+        <v>0.2392698818277861</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.899099837907799</v>
+        <v>0.6336037236600173</v>
       </c>
       <c r="D3" t="n">
-        <v>16.67964032755869</v>
+        <v>2.710441553228287</v>
       </c>
       <c r="E3" t="n">
-        <v>7.014961156559708</v>
+        <v>1.139931187940953</v>
       </c>
       <c r="F3" t="n">
-        <v>1.472430042017145</v>
+        <v>0.2392698818277861</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.96089076920638</v>
+        <v>3.243644749996037</v>
       </c>
       <c r="D4" t="n">
-        <v>20.21251166900912</v>
+        <v>3.284533146213982</v>
       </c>
       <c r="E4" t="n">
-        <v>7.014961156559708</v>
+        <v>1.139931187940953</v>
       </c>
       <c r="F4" t="n">
-        <v>1.472430042017145</v>
+        <v>0.2392698818277861</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
